--- a/Starfront/文档/配置表/BattleSceneCellResource.xlsx
+++ b/Starfront/文档/配置表/BattleSceneCellResource.xlsx
@@ -1241,9 +1241,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G345"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4910,6 +4910,4281 @@
       </c>
       <c r="G174" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="175" ht="16.5" spans="1:7">
+      <c r="A175" s="4"/>
+      <c r="B175" s="4">
+        <v>1002001</v>
+      </c>
+      <c r="C175" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D175" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E175" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="1:7">
+      <c r="A176" s="4"/>
+      <c r="B176" s="4">
+        <v>1002002</v>
+      </c>
+      <c r="C176" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D176" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E176" s="4">
+        <v>-13</v>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="16.5" spans="1:7">
+      <c r="A177" s="4"/>
+      <c r="B177" s="4">
+        <v>1002003</v>
+      </c>
+      <c r="C177" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D177" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E177" s="4">
+        <v>-11</v>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="1:7">
+      <c r="A178" s="4"/>
+      <c r="B178" s="4">
+        <v>1002004</v>
+      </c>
+      <c r="C178" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D178" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E178" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="1:7">
+      <c r="A179" s="4"/>
+      <c r="B179" s="4">
+        <v>1002005</v>
+      </c>
+      <c r="C179" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D179" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E179" s="4">
+        <v>-7</v>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="1:7">
+      <c r="A180" s="4"/>
+      <c r="B180" s="4">
+        <v>1002006</v>
+      </c>
+      <c r="C180" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D180" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E180" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="16.5" spans="1:7">
+      <c r="A181" s="4"/>
+      <c r="B181" s="4">
+        <v>1002007</v>
+      </c>
+      <c r="C181" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D181" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E181" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="16.5" spans="1:7">
+      <c r="A182" s="4"/>
+      <c r="B182" s="4">
+        <v>1002008</v>
+      </c>
+      <c r="C182" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D182" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E182" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="16.5" spans="1:7">
+      <c r="A183" s="4"/>
+      <c r="B183" s="4">
+        <v>1002009</v>
+      </c>
+      <c r="C183" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D183" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E183" s="4">
+        <v>1</v>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="16.5" spans="1:7">
+      <c r="A184" s="4"/>
+      <c r="B184" s="4">
+        <v>1002010</v>
+      </c>
+      <c r="C184" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D184" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E184" s="4">
+        <v>3</v>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="16.5" spans="1:7">
+      <c r="A185" s="4"/>
+      <c r="B185" s="4">
+        <v>1002011</v>
+      </c>
+      <c r="C185" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D185" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E185" s="4">
+        <v>5</v>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="16.5" spans="1:7">
+      <c r="A186" s="4"/>
+      <c r="B186" s="4">
+        <v>1002012</v>
+      </c>
+      <c r="C186" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D186" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E186" s="4">
+        <v>7</v>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="16.5" spans="1:7">
+      <c r="A187" s="4"/>
+      <c r="B187" s="4">
+        <v>1002013</v>
+      </c>
+      <c r="C187" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D187" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E187" s="4">
+        <v>9</v>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="16.5" spans="1:7">
+      <c r="A188" s="4"/>
+      <c r="B188" s="4">
+        <v>1002014</v>
+      </c>
+      <c r="C188" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D188" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E188" s="4">
+        <v>11</v>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="16.5" spans="1:7">
+      <c r="A189" s="4"/>
+      <c r="B189" s="4">
+        <v>1002015</v>
+      </c>
+      <c r="C189" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D189" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E189" s="4">
+        <v>13</v>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="16.5" spans="1:7">
+      <c r="A190" s="4"/>
+      <c r="B190" s="4">
+        <v>1002016</v>
+      </c>
+      <c r="C190" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D190" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E190" s="4">
+        <v>15</v>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="16.5" spans="1:7">
+      <c r="A191" s="4"/>
+      <c r="B191" s="4">
+        <v>1002017</v>
+      </c>
+      <c r="C191" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D191" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E191" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="16.5" spans="1:7">
+      <c r="A192" s="4"/>
+      <c r="B192" s="4">
+        <v>1002018</v>
+      </c>
+      <c r="C192" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D192" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E192" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="16.5" spans="1:7">
+      <c r="A193" s="4"/>
+      <c r="B193" s="4">
+        <v>1002019</v>
+      </c>
+      <c r="C193" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D193" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E193" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="16.5" spans="1:7">
+      <c r="A194" s="4"/>
+      <c r="B194" s="4">
+        <v>1002020</v>
+      </c>
+      <c r="C194" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D194" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E194" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16.5" spans="1:7">
+      <c r="A195" s="4"/>
+      <c r="B195" s="4">
+        <v>1002021</v>
+      </c>
+      <c r="C195" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D195" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E195" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="16.5" spans="1:7">
+      <c r="A196" s="4"/>
+      <c r="B196" s="4">
+        <v>1002022</v>
+      </c>
+      <c r="C196" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D196" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E196" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="16.5" spans="1:7">
+      <c r="A197" s="4"/>
+      <c r="B197" s="4">
+        <v>1002023</v>
+      </c>
+      <c r="C197" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D197" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E197" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="16.5" spans="1:7">
+      <c r="A198" s="4"/>
+      <c r="B198" s="4">
+        <v>1002024</v>
+      </c>
+      <c r="C198" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D198" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E198" s="4">
+        <v>0</v>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="16.5" spans="1:7">
+      <c r="A199" s="4"/>
+      <c r="B199" s="4">
+        <v>1002025</v>
+      </c>
+      <c r="C199" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D199" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E199" s="4">
+        <v>2</v>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16.5" spans="1:7">
+      <c r="A200" s="4"/>
+      <c r="B200" s="4">
+        <v>1002026</v>
+      </c>
+      <c r="C200" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D200" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E200" s="4">
+        <v>4</v>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="16.5" spans="1:7">
+      <c r="A201" s="4"/>
+      <c r="B201" s="4">
+        <v>1002027</v>
+      </c>
+      <c r="C201" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D201" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E201" s="4">
+        <v>6</v>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="16.5" spans="1:7">
+      <c r="A202" s="4"/>
+      <c r="B202" s="4">
+        <v>1002028</v>
+      </c>
+      <c r="C202" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D202" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E202" s="4">
+        <v>8</v>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="16.5" spans="1:7">
+      <c r="A203" s="4"/>
+      <c r="B203" s="4">
+        <v>1002029</v>
+      </c>
+      <c r="C203" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D203" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E203" s="4">
+        <v>10</v>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="16.5" spans="1:7">
+      <c r="A204" s="4"/>
+      <c r="B204" s="4">
+        <v>1002030</v>
+      </c>
+      <c r="C204" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D204" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E204" s="4">
+        <v>12</v>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="16.5" spans="1:7">
+      <c r="A205" s="4"/>
+      <c r="B205" s="4">
+        <v>1002031</v>
+      </c>
+      <c r="C205" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D205" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E205" s="4">
+        <v>14</v>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="16.5" spans="1:7">
+      <c r="A206" s="4"/>
+      <c r="B206" s="4">
+        <v>1002032</v>
+      </c>
+      <c r="C206" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D206" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E206" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="16.5" spans="1:7">
+      <c r="A207" s="4"/>
+      <c r="B207" s="4">
+        <v>1002033</v>
+      </c>
+      <c r="C207" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D207" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E207" s="4">
+        <v>-13</v>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="16.5" spans="1:7">
+      <c r="A208" s="4"/>
+      <c r="B208" s="4">
+        <v>1002034</v>
+      </c>
+      <c r="C208" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D208" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E208" s="4">
+        <v>-11</v>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="16.5" spans="1:7">
+      <c r="A209" s="4"/>
+      <c r="B209" s="4">
+        <v>1002035</v>
+      </c>
+      <c r="C209" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D209" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E209" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="16.5" spans="1:7">
+      <c r="A210" s="4"/>
+      <c r="B210" s="4">
+        <v>1002036</v>
+      </c>
+      <c r="C210" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D210" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E210" s="4">
+        <v>-7</v>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="16.5" spans="1:7">
+      <c r="A211" s="4"/>
+      <c r="B211" s="4">
+        <v>1002037</v>
+      </c>
+      <c r="C211" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D211" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E211" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="16.5" spans="1:7">
+      <c r="A212" s="4"/>
+      <c r="B212" s="4">
+        <v>1002038</v>
+      </c>
+      <c r="C212" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D212" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E212" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="16.5" spans="1:7">
+      <c r="A213" s="4"/>
+      <c r="B213" s="4">
+        <v>1002039</v>
+      </c>
+      <c r="C213" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D213" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E213" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="16.5" spans="1:7">
+      <c r="A214" s="4"/>
+      <c r="B214" s="4">
+        <v>1002040</v>
+      </c>
+      <c r="C214" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D214" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E214" s="4">
+        <v>1</v>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="16.5" spans="1:7">
+      <c r="A215" s="4"/>
+      <c r="B215" s="4">
+        <v>1002041</v>
+      </c>
+      <c r="C215" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D215" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E215" s="4">
+        <v>3</v>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="16.5" spans="1:7">
+      <c r="A216" s="4"/>
+      <c r="B216" s="4">
+        <v>1002042</v>
+      </c>
+      <c r="C216" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D216" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E216" s="4">
+        <v>5</v>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="16.5" spans="1:7">
+      <c r="A217" s="4"/>
+      <c r="B217" s="4">
+        <v>1002043</v>
+      </c>
+      <c r="C217" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D217" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E217" s="4">
+        <v>7</v>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="16.5" spans="1:7">
+      <c r="A218" s="4"/>
+      <c r="B218" s="4">
+        <v>1002044</v>
+      </c>
+      <c r="C218" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D218" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E218" s="4">
+        <v>9</v>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="16.5" spans="1:7">
+      <c r="A219" s="4"/>
+      <c r="B219" s="4">
+        <v>1002045</v>
+      </c>
+      <c r="C219" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D219" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E219" s="4">
+        <v>11</v>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="16.5" spans="1:7">
+      <c r="A220" s="4"/>
+      <c r="B220" s="4">
+        <v>1002046</v>
+      </c>
+      <c r="C220" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D220" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E220" s="4">
+        <v>13</v>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="16.5" spans="1:7">
+      <c r="A221" s="4"/>
+      <c r="B221" s="4">
+        <v>1002047</v>
+      </c>
+      <c r="C221" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D221" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E221" s="4">
+        <v>15</v>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16.5" spans="1:7">
+      <c r="A222" s="4"/>
+      <c r="B222" s="4">
+        <v>1002048</v>
+      </c>
+      <c r="C222" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D222" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E222" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="16.5" spans="1:7">
+      <c r="A223" s="4"/>
+      <c r="B223" s="4">
+        <v>1002049</v>
+      </c>
+      <c r="C223" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D223" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E223" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="16.5" spans="1:7">
+      <c r="A224" s="4"/>
+      <c r="B224" s="4">
+        <v>1002050</v>
+      </c>
+      <c r="C224" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D224" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E224" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="16.5" spans="1:7">
+      <c r="A225" s="4"/>
+      <c r="B225" s="4">
+        <v>1002051</v>
+      </c>
+      <c r="C225" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D225" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E225" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="16.5" spans="1:7">
+      <c r="A226" s="4"/>
+      <c r="B226" s="4">
+        <v>1002052</v>
+      </c>
+      <c r="C226" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D226" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E226" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="16.5" spans="1:7">
+      <c r="A227" s="4"/>
+      <c r="B227" s="4">
+        <v>1002053</v>
+      </c>
+      <c r="C227" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D227" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E227" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="16.5" spans="1:7">
+      <c r="A228" s="4"/>
+      <c r="B228" s="4">
+        <v>1002054</v>
+      </c>
+      <c r="C228" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D228" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E228" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="16.5" spans="1:7">
+      <c r="A229" s="4"/>
+      <c r="B229" s="4">
+        <v>1002055</v>
+      </c>
+      <c r="C229" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D229" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E229" s="4">
+        <v>0</v>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="16.5" spans="1:7">
+      <c r="A230" s="4"/>
+      <c r="B230" s="4">
+        <v>1002056</v>
+      </c>
+      <c r="C230" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D230" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E230" s="4">
+        <v>2</v>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="16.5" spans="1:7">
+      <c r="A231" s="4"/>
+      <c r="B231" s="4">
+        <v>1002057</v>
+      </c>
+      <c r="C231" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D231" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E231" s="4">
+        <v>4</v>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="16.5" spans="1:7">
+      <c r="A232" s="4"/>
+      <c r="B232" s="4">
+        <v>1002058</v>
+      </c>
+      <c r="C232" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D232" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E232" s="4">
+        <v>6</v>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="16.5" spans="1:7">
+      <c r="A233" s="4"/>
+      <c r="B233" s="4">
+        <v>1002059</v>
+      </c>
+      <c r="C233" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D233" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E233" s="4">
+        <v>8</v>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="16.5" spans="1:7">
+      <c r="A234" s="4"/>
+      <c r="B234" s="4">
+        <v>1002060</v>
+      </c>
+      <c r="C234" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D234" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E234" s="4">
+        <v>10</v>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="16.5" spans="1:7">
+      <c r="A235" s="4"/>
+      <c r="B235" s="4">
+        <v>1002061</v>
+      </c>
+      <c r="C235" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D235" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E235" s="4">
+        <v>12</v>
+      </c>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="16.5" spans="1:7">
+      <c r="A236" s="4"/>
+      <c r="B236" s="4">
+        <v>1002062</v>
+      </c>
+      <c r="C236" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D236" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E236" s="4">
+        <v>14</v>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="16.5" spans="1:7">
+      <c r="A237" s="4"/>
+      <c r="B237" s="4">
+        <v>1002063</v>
+      </c>
+      <c r="C237" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D237" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E237" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="16.5" spans="1:7">
+      <c r="A238" s="4"/>
+      <c r="B238" s="4">
+        <v>1002064</v>
+      </c>
+      <c r="C238" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D238" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E238" s="4">
+        <v>-13</v>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="16.5" spans="1:7">
+      <c r="A239" s="4"/>
+      <c r="B239" s="4">
+        <v>1002065</v>
+      </c>
+      <c r="C239" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D239" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E239" s="4">
+        <v>-11</v>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="16.5" spans="1:7">
+      <c r="A240" s="4"/>
+      <c r="B240" s="4">
+        <v>1002066</v>
+      </c>
+      <c r="C240" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D240" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E240" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="16.5" spans="1:7">
+      <c r="A241" s="4"/>
+      <c r="B241" s="4">
+        <v>1002067</v>
+      </c>
+      <c r="C241" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D241" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E241" s="4">
+        <v>-7</v>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="16.5" spans="1:7">
+      <c r="A242" s="4"/>
+      <c r="B242" s="4">
+        <v>1002068</v>
+      </c>
+      <c r="C242" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D242" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E242" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="16.5" spans="1:7">
+      <c r="A243" s="4"/>
+      <c r="B243" s="4">
+        <v>1002069</v>
+      </c>
+      <c r="C243" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D243" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E243" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="16.5" spans="1:7">
+      <c r="A244" s="4"/>
+      <c r="B244" s="4">
+        <v>1002070</v>
+      </c>
+      <c r="C244" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D244" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E244" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="16.5" spans="1:7">
+      <c r="A245" s="4"/>
+      <c r="B245" s="4">
+        <v>1002071</v>
+      </c>
+      <c r="C245" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D245" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E245" s="4">
+        <v>1</v>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="16.5" spans="1:7">
+      <c r="A246" s="4"/>
+      <c r="B246" s="4">
+        <v>1002072</v>
+      </c>
+      <c r="C246" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D246" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E246" s="4">
+        <v>3</v>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="16.5" spans="1:7">
+      <c r="A247" s="4"/>
+      <c r="B247" s="4">
+        <v>1002073</v>
+      </c>
+      <c r="C247" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D247" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E247" s="4">
+        <v>5</v>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="16.5" spans="1:7">
+      <c r="A248" s="4"/>
+      <c r="B248" s="4">
+        <v>1002074</v>
+      </c>
+      <c r="C248" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D248" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E248" s="4">
+        <v>7</v>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="16.5" spans="1:7">
+      <c r="A249" s="4"/>
+      <c r="B249" s="4">
+        <v>1002075</v>
+      </c>
+      <c r="C249" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D249" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E249" s="4">
+        <v>9</v>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="16.5" spans="1:7">
+      <c r="A250" s="4"/>
+      <c r="B250" s="4">
+        <v>1002076</v>
+      </c>
+      <c r="C250" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D250" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E250" s="4">
+        <v>11</v>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="16.5" spans="1:7">
+      <c r="A251" s="4"/>
+      <c r="B251" s="4">
+        <v>1002077</v>
+      </c>
+      <c r="C251" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D251" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E251" s="4">
+        <v>13</v>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="16.5" spans="1:7">
+      <c r="A252" s="4"/>
+      <c r="B252" s="4">
+        <v>1002078</v>
+      </c>
+      <c r="C252" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D252" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E252" s="4">
+        <v>15</v>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="16.5" spans="1:7">
+      <c r="A253" s="4"/>
+      <c r="B253" s="4">
+        <v>1002079</v>
+      </c>
+      <c r="C253" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D253" s="4">
+        <v>0</v>
+      </c>
+      <c r="E253" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="16.5" spans="1:7">
+      <c r="A254" s="4"/>
+      <c r="B254" s="4">
+        <v>1002080</v>
+      </c>
+      <c r="C254" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D254" s="4">
+        <v>0</v>
+      </c>
+      <c r="E254" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="16.5" spans="1:7">
+      <c r="A255" s="4"/>
+      <c r="B255" s="4">
+        <v>1002081</v>
+      </c>
+      <c r="C255" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D255" s="4">
+        <v>0</v>
+      </c>
+      <c r="E255" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="16.5" spans="1:7">
+      <c r="A256" s="4"/>
+      <c r="B256" s="4">
+        <v>1002082</v>
+      </c>
+      <c r="C256" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D256" s="4">
+        <v>0</v>
+      </c>
+      <c r="E256" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="16.5" spans="1:7">
+      <c r="A257" s="4"/>
+      <c r="B257" s="4">
+        <v>1002083</v>
+      </c>
+      <c r="C257" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D257" s="4">
+        <v>0</v>
+      </c>
+      <c r="E257" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="16.5" spans="1:7">
+      <c r="A258" s="4"/>
+      <c r="B258" s="4">
+        <v>1002084</v>
+      </c>
+      <c r="C258" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D258" s="4">
+        <v>0</v>
+      </c>
+      <c r="E258" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="16.5" spans="1:7">
+      <c r="A259" s="4"/>
+      <c r="B259" s="4">
+        <v>1002085</v>
+      </c>
+      <c r="C259" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D259" s="4">
+        <v>0</v>
+      </c>
+      <c r="E259" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="16.5" spans="1:7">
+      <c r="A260" s="4"/>
+      <c r="B260" s="4">
+        <v>1002086</v>
+      </c>
+      <c r="C260" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D260" s="4">
+        <v>0</v>
+      </c>
+      <c r="E260" s="4">
+        <v>0</v>
+      </c>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="16.5" spans="1:7">
+      <c r="A261" s="4"/>
+      <c r="B261" s="4">
+        <v>1002087</v>
+      </c>
+      <c r="C261" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D261" s="4">
+        <v>0</v>
+      </c>
+      <c r="E261" s="4">
+        <v>2</v>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="16.5" spans="1:7">
+      <c r="A262" s="4"/>
+      <c r="B262" s="4">
+        <v>1002088</v>
+      </c>
+      <c r="C262" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D262" s="4">
+        <v>0</v>
+      </c>
+      <c r="E262" s="4">
+        <v>4</v>
+      </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="16.5" spans="1:7">
+      <c r="A263" s="4"/>
+      <c r="B263" s="4">
+        <v>1002089</v>
+      </c>
+      <c r="C263" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D263" s="4">
+        <v>0</v>
+      </c>
+      <c r="E263" s="4">
+        <v>6</v>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="16.5" spans="1:7">
+      <c r="A264" s="4"/>
+      <c r="B264" s="4">
+        <v>1002090</v>
+      </c>
+      <c r="C264" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D264" s="4">
+        <v>0</v>
+      </c>
+      <c r="E264" s="4">
+        <v>8</v>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="16.5" spans="1:7">
+      <c r="A265" s="4"/>
+      <c r="B265" s="4">
+        <v>1002091</v>
+      </c>
+      <c r="C265" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D265" s="4">
+        <v>0</v>
+      </c>
+      <c r="E265" s="4">
+        <v>10</v>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="16.5" spans="1:7">
+      <c r="A266" s="4"/>
+      <c r="B266" s="4">
+        <v>1002092</v>
+      </c>
+      <c r="C266" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D266" s="4">
+        <v>0</v>
+      </c>
+      <c r="E266" s="4">
+        <v>12</v>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="16.5" spans="1:7">
+      <c r="A267" s="4"/>
+      <c r="B267" s="4">
+        <v>1002093</v>
+      </c>
+      <c r="C267" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D267" s="4">
+        <v>0</v>
+      </c>
+      <c r="E267" s="4">
+        <v>14</v>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="16.5" spans="1:7">
+      <c r="A268" s="4"/>
+      <c r="B268" s="4">
+        <v>1002094</v>
+      </c>
+      <c r="C268" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D268" s="4">
+        <v>1</v>
+      </c>
+      <c r="E268" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="16.5" spans="1:7">
+      <c r="A269" s="4"/>
+      <c r="B269" s="4">
+        <v>1002095</v>
+      </c>
+      <c r="C269" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D269" s="4">
+        <v>1</v>
+      </c>
+      <c r="E269" s="4">
+        <v>-13</v>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="16.5" spans="1:7">
+      <c r="A270" s="4"/>
+      <c r="B270" s="4">
+        <v>1002096</v>
+      </c>
+      <c r="C270" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D270" s="4">
+        <v>1</v>
+      </c>
+      <c r="E270" s="4">
+        <v>-11</v>
+      </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="16.5" spans="1:7">
+      <c r="A271" s="4"/>
+      <c r="B271" s="4">
+        <v>1002097</v>
+      </c>
+      <c r="C271" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D271" s="4">
+        <v>1</v>
+      </c>
+      <c r="E271" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="16.5" spans="1:7">
+      <c r="A272" s="4"/>
+      <c r="B272" s="4">
+        <v>1002098</v>
+      </c>
+      <c r="C272" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D272" s="4">
+        <v>1</v>
+      </c>
+      <c r="E272" s="4">
+        <v>-7</v>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="16.5" spans="1:7">
+      <c r="A273" s="4"/>
+      <c r="B273" s="4">
+        <v>1002099</v>
+      </c>
+      <c r="C273" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D273" s="4">
+        <v>1</v>
+      </c>
+      <c r="E273" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="16.5" spans="1:7">
+      <c r="A274" s="4"/>
+      <c r="B274" s="4">
+        <v>1002100</v>
+      </c>
+      <c r="C274" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D274" s="4">
+        <v>1</v>
+      </c>
+      <c r="E274" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="16.5" spans="1:7">
+      <c r="A275" s="4"/>
+      <c r="B275" s="4">
+        <v>1002101</v>
+      </c>
+      <c r="C275" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D275" s="4">
+        <v>1</v>
+      </c>
+      <c r="E275" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="16.5" spans="1:7">
+      <c r="A276" s="4"/>
+      <c r="B276" s="4">
+        <v>1002102</v>
+      </c>
+      <c r="C276" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D276" s="4">
+        <v>1</v>
+      </c>
+      <c r="E276" s="4">
+        <v>1</v>
+      </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="16.5" spans="1:7">
+      <c r="A277" s="4"/>
+      <c r="B277" s="4">
+        <v>1002103</v>
+      </c>
+      <c r="C277" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D277" s="4">
+        <v>1</v>
+      </c>
+      <c r="E277" s="4">
+        <v>3</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="16.5" spans="1:7">
+      <c r="A278" s="4"/>
+      <c r="B278" s="4">
+        <v>1002104</v>
+      </c>
+      <c r="C278" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D278" s="4">
+        <v>1</v>
+      </c>
+      <c r="E278" s="4">
+        <v>5</v>
+      </c>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="16.5" spans="1:7">
+      <c r="A279" s="4"/>
+      <c r="B279" s="4">
+        <v>1002105</v>
+      </c>
+      <c r="C279" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D279" s="4">
+        <v>1</v>
+      </c>
+      <c r="E279" s="4">
+        <v>7</v>
+      </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="16.5" spans="1:7">
+      <c r="A280" s="4"/>
+      <c r="B280" s="4">
+        <v>1002106</v>
+      </c>
+      <c r="C280" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D280" s="4">
+        <v>1</v>
+      </c>
+      <c r="E280" s="4">
+        <v>9</v>
+      </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="16.5" spans="1:7">
+      <c r="A281" s="4"/>
+      <c r="B281" s="4">
+        <v>1002107</v>
+      </c>
+      <c r="C281" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D281" s="4">
+        <v>1</v>
+      </c>
+      <c r="E281" s="4">
+        <v>11</v>
+      </c>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="16.5" spans="1:7">
+      <c r="A282" s="4"/>
+      <c r="B282" s="4">
+        <v>1002108</v>
+      </c>
+      <c r="C282" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D282" s="4">
+        <v>1</v>
+      </c>
+      <c r="E282" s="4">
+        <v>13</v>
+      </c>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="16.5" spans="1:7">
+      <c r="A283" s="4"/>
+      <c r="B283" s="4">
+        <v>1002109</v>
+      </c>
+      <c r="C283" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D283" s="4">
+        <v>1</v>
+      </c>
+      <c r="E283" s="4">
+        <v>15</v>
+      </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="16.5" spans="1:7">
+      <c r="A284" s="4"/>
+      <c r="B284" s="4">
+        <v>1002110</v>
+      </c>
+      <c r="C284" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D284" s="4">
+        <v>2</v>
+      </c>
+      <c r="E284" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G284" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="16.5" spans="1:7">
+      <c r="A285" s="4"/>
+      <c r="B285" s="4">
+        <v>1002111</v>
+      </c>
+      <c r="C285" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D285" s="4">
+        <v>2</v>
+      </c>
+      <c r="E285" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="16.5" spans="1:7">
+      <c r="A286" s="4"/>
+      <c r="B286" s="4">
+        <v>1002112</v>
+      </c>
+      <c r="C286" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D286" s="4">
+        <v>2</v>
+      </c>
+      <c r="E286" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="16.5" spans="1:7">
+      <c r="A287" s="4"/>
+      <c r="B287" s="4">
+        <v>1002113</v>
+      </c>
+      <c r="C287" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D287" s="4">
+        <v>2</v>
+      </c>
+      <c r="E287" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="16.5" spans="1:7">
+      <c r="A288" s="4"/>
+      <c r="B288" s="4">
+        <v>1002114</v>
+      </c>
+      <c r="C288" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D288" s="4">
+        <v>2</v>
+      </c>
+      <c r="E288" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="16.5" spans="1:7">
+      <c r="A289" s="4"/>
+      <c r="B289" s="4">
+        <v>1002115</v>
+      </c>
+      <c r="C289" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D289" s="4">
+        <v>2</v>
+      </c>
+      <c r="E289" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="16.5" spans="1:7">
+      <c r="A290" s="4"/>
+      <c r="B290" s="4">
+        <v>1002116</v>
+      </c>
+      <c r="C290" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D290" s="4">
+        <v>2</v>
+      </c>
+      <c r="E290" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="16.5" spans="1:7">
+      <c r="A291" s="4"/>
+      <c r="B291" s="4">
+        <v>1002117</v>
+      </c>
+      <c r="C291" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D291" s="4">
+        <v>2</v>
+      </c>
+      <c r="E291" s="4">
+        <v>0</v>
+      </c>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G291" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="16.5" spans="1:7">
+      <c r="A292" s="4"/>
+      <c r="B292" s="4">
+        <v>1002118</v>
+      </c>
+      <c r="C292" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D292" s="4">
+        <v>2</v>
+      </c>
+      <c r="E292" s="4">
+        <v>2</v>
+      </c>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="16.5" spans="1:7">
+      <c r="A293" s="4"/>
+      <c r="B293" s="4">
+        <v>1002119</v>
+      </c>
+      <c r="C293" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D293" s="4">
+        <v>2</v>
+      </c>
+      <c r="E293" s="4">
+        <v>4</v>
+      </c>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G293" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="16.5" spans="1:7">
+      <c r="A294" s="4"/>
+      <c r="B294" s="4">
+        <v>1002120</v>
+      </c>
+      <c r="C294" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D294" s="4">
+        <v>2</v>
+      </c>
+      <c r="E294" s="4">
+        <v>6</v>
+      </c>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="16.5" spans="1:7">
+      <c r="A295" s="4"/>
+      <c r="B295" s="4">
+        <v>1002121</v>
+      </c>
+      <c r="C295" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D295" s="4">
+        <v>2</v>
+      </c>
+      <c r="E295" s="4">
+        <v>8</v>
+      </c>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G295" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="16.5" spans="1:7">
+      <c r="A296" s="4"/>
+      <c r="B296" s="4">
+        <v>1002122</v>
+      </c>
+      <c r="C296" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D296" s="4">
+        <v>2</v>
+      </c>
+      <c r="E296" s="4">
+        <v>10</v>
+      </c>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="16.5" spans="1:7">
+      <c r="A297" s="4"/>
+      <c r="B297" s="4">
+        <v>1002123</v>
+      </c>
+      <c r="C297" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D297" s="4">
+        <v>2</v>
+      </c>
+      <c r="E297" s="4">
+        <v>12</v>
+      </c>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="16.5" spans="1:7">
+      <c r="A298" s="4"/>
+      <c r="B298" s="4">
+        <v>1002124</v>
+      </c>
+      <c r="C298" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D298" s="4">
+        <v>2</v>
+      </c>
+      <c r="E298" s="4">
+        <v>14</v>
+      </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="16.5" spans="1:7">
+      <c r="A299" s="4"/>
+      <c r="B299" s="4">
+        <v>1002125</v>
+      </c>
+      <c r="C299" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D299" s="4">
+        <v>3</v>
+      </c>
+      <c r="E299" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="16.5" spans="1:7">
+      <c r="A300" s="4"/>
+      <c r="B300" s="4">
+        <v>1002126</v>
+      </c>
+      <c r="C300" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D300" s="4">
+        <v>3</v>
+      </c>
+      <c r="E300" s="4">
+        <v>-13</v>
+      </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="16.5" spans="1:7">
+      <c r="A301" s="4"/>
+      <c r="B301" s="4">
+        <v>1002127</v>
+      </c>
+      <c r="C301" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D301" s="4">
+        <v>3</v>
+      </c>
+      <c r="E301" s="4">
+        <v>-11</v>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="16.5" spans="1:7">
+      <c r="A302" s="4"/>
+      <c r="B302" s="4">
+        <v>1002128</v>
+      </c>
+      <c r="C302" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D302" s="4">
+        <v>3</v>
+      </c>
+      <c r="E302" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="16.5" spans="1:7">
+      <c r="A303" s="4"/>
+      <c r="B303" s="4">
+        <v>1002129</v>
+      </c>
+      <c r="C303" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D303" s="4">
+        <v>3</v>
+      </c>
+      <c r="E303" s="4">
+        <v>-7</v>
+      </c>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G303" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="16.5" spans="1:7">
+      <c r="A304" s="4"/>
+      <c r="B304" s="4">
+        <v>1002130</v>
+      </c>
+      <c r="C304" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D304" s="4">
+        <v>3</v>
+      </c>
+      <c r="E304" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="16.5" spans="1:7">
+      <c r="A305" s="4"/>
+      <c r="B305" s="4">
+        <v>1002131</v>
+      </c>
+      <c r="C305" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D305" s="4">
+        <v>3</v>
+      </c>
+      <c r="E305" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G305" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="16.5" spans="1:7">
+      <c r="A306" s="4"/>
+      <c r="B306" s="4">
+        <v>1002132</v>
+      </c>
+      <c r="C306" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D306" s="4">
+        <v>3</v>
+      </c>
+      <c r="E306" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="16.5" spans="1:7">
+      <c r="A307" s="4"/>
+      <c r="B307" s="4">
+        <v>1002133</v>
+      </c>
+      <c r="C307" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D307" s="4">
+        <v>3</v>
+      </c>
+      <c r="E307" s="4">
+        <v>1</v>
+      </c>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="16.5" spans="1:7">
+      <c r="A308" s="4"/>
+      <c r="B308" s="4">
+        <v>1002134</v>
+      </c>
+      <c r="C308" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D308" s="4">
+        <v>3</v>
+      </c>
+      <c r="E308" s="4">
+        <v>3</v>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="16.5" spans="1:7">
+      <c r="A309" s="4"/>
+      <c r="B309" s="4">
+        <v>1002135</v>
+      </c>
+      <c r="C309" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D309" s="4">
+        <v>3</v>
+      </c>
+      <c r="E309" s="4">
+        <v>5</v>
+      </c>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G309" s="4" t="inlineStr">
+        <is>
+          <t>水洼</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="16.5" spans="1:7">
+      <c r="A310" s="4"/>
+      <c r="B310" s="4">
+        <v>1002136</v>
+      </c>
+      <c r="C310" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D310" s="4">
+        <v>3</v>
+      </c>
+      <c r="E310" s="4">
+        <v>7</v>
+      </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="16.5" spans="1:7">
+      <c r="A311" s="4"/>
+      <c r="B311" s="4">
+        <v>1002137</v>
+      </c>
+      <c r="C311" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D311" s="4">
+        <v>3</v>
+      </c>
+      <c r="E311" s="4">
+        <v>9</v>
+      </c>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G311" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="16.5" spans="1:7">
+      <c r="A312" s="4"/>
+      <c r="B312" s="4">
+        <v>1002138</v>
+      </c>
+      <c r="C312" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D312" s="4">
+        <v>3</v>
+      </c>
+      <c r="E312" s="4">
+        <v>11</v>
+      </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G312" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="16.5" spans="1:7">
+      <c r="A313" s="4"/>
+      <c r="B313" s="4">
+        <v>1002139</v>
+      </c>
+      <c r="C313" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D313" s="4">
+        <v>3</v>
+      </c>
+      <c r="E313" s="4">
+        <v>13</v>
+      </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="16.5" spans="1:7">
+      <c r="A314" s="4"/>
+      <c r="B314" s="4">
+        <v>1002140</v>
+      </c>
+      <c r="C314" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D314" s="4">
+        <v>3</v>
+      </c>
+      <c r="E314" s="4">
+        <v>15</v>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="16.5" spans="1:7">
+      <c r="A315" s="4"/>
+      <c r="B315" s="4">
+        <v>1002141</v>
+      </c>
+      <c r="C315" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D315" s="4">
+        <v>4</v>
+      </c>
+      <c r="E315" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G315" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="16.5" spans="1:7">
+      <c r="A316" s="4"/>
+      <c r="B316" s="4">
+        <v>1002142</v>
+      </c>
+      <c r="C316" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D316" s="4">
+        <v>4</v>
+      </c>
+      <c r="E316" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="16.5" spans="1:7">
+      <c r="A317" s="4"/>
+      <c r="B317" s="4">
+        <v>1002143</v>
+      </c>
+      <c r="C317" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D317" s="4">
+        <v>4</v>
+      </c>
+      <c r="E317" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G317" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="16.5" spans="1:7">
+      <c r="A318" s="4"/>
+      <c r="B318" s="4">
+        <v>1002144</v>
+      </c>
+      <c r="C318" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D318" s="4">
+        <v>4</v>
+      </c>
+      <c r="E318" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G318" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="16.5" spans="1:7">
+      <c r="A319" s="4"/>
+      <c r="B319" s="4">
+        <v>1002145</v>
+      </c>
+      <c r="C319" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D319" s="4">
+        <v>4</v>
+      </c>
+      <c r="E319" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G319" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="16.5" spans="1:7">
+      <c r="A320" s="4"/>
+      <c r="B320" s="4">
+        <v>1002146</v>
+      </c>
+      <c r="C320" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D320" s="4">
+        <v>4</v>
+      </c>
+      <c r="E320" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G320" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="16.5" spans="1:7">
+      <c r="A321" s="4"/>
+      <c r="B321" s="4">
+        <v>1002147</v>
+      </c>
+      <c r="C321" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D321" s="4">
+        <v>4</v>
+      </c>
+      <c r="E321" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="16.5" spans="1:7">
+      <c r="A322" s="4"/>
+      <c r="B322" s="4">
+        <v>1002148</v>
+      </c>
+      <c r="C322" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D322" s="4">
+        <v>4</v>
+      </c>
+      <c r="E322" s="4">
+        <v>0</v>
+      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="16.5" spans="1:7">
+      <c r="A323" s="4"/>
+      <c r="B323" s="4">
+        <v>1002149</v>
+      </c>
+      <c r="C323" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D323" s="4">
+        <v>4</v>
+      </c>
+      <c r="E323" s="4">
+        <v>2</v>
+      </c>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="16.5" spans="1:7">
+      <c r="A324" s="4"/>
+      <c r="B324" s="4">
+        <v>1002150</v>
+      </c>
+      <c r="C324" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D324" s="4">
+        <v>4</v>
+      </c>
+      <c r="E324" s="4">
+        <v>4</v>
+      </c>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="16.5" spans="1:7">
+      <c r="A325" s="4"/>
+      <c r="B325" s="4">
+        <v>1002151</v>
+      </c>
+      <c r="C325" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D325" s="4">
+        <v>4</v>
+      </c>
+      <c r="E325" s="4">
+        <v>6</v>
+      </c>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="16.5" spans="1:7">
+      <c r="A326" s="4"/>
+      <c r="B326" s="4">
+        <v>1002152</v>
+      </c>
+      <c r="C326" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D326" s="4">
+        <v>4</v>
+      </c>
+      <c r="E326" s="4">
+        <v>8</v>
+      </c>
+      <c r="F326" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G326" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="16.5" spans="1:7">
+      <c r="A327" s="4"/>
+      <c r="B327" s="4">
+        <v>1002153</v>
+      </c>
+      <c r="C327" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D327" s="4">
+        <v>4</v>
+      </c>
+      <c r="E327" s="4">
+        <v>10</v>
+      </c>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>绝对中立</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>山体</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="16.5" spans="1:7">
+      <c r="A328" s="4"/>
+      <c r="B328" s="4">
+        <v>1002154</v>
+      </c>
+      <c r="C328" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D328" s="4">
+        <v>4</v>
+      </c>
+      <c r="E328" s="4">
+        <v>12</v>
+      </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="16.5" spans="1:7">
+      <c r="A329" s="4"/>
+      <c r="B329" s="4">
+        <v>1002155</v>
+      </c>
+      <c r="C329" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D329" s="4">
+        <v>4</v>
+      </c>
+      <c r="E329" s="4">
+        <v>14</v>
+      </c>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G329" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="16.5" spans="1:7">
+      <c r="A330" s="4"/>
+      <c r="B330" s="4">
+        <v>1002156</v>
+      </c>
+      <c r="C330" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D330" s="4">
+        <v>5</v>
+      </c>
+      <c r="E330" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="16.5" spans="1:7">
+      <c r="A331" s="4"/>
+      <c r="B331" s="4">
+        <v>1002157</v>
+      </c>
+      <c r="C331" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D331" s="4">
+        <v>5</v>
+      </c>
+      <c r="E331" s="4">
+        <v>-13</v>
+      </c>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="16.5" spans="1:7">
+      <c r="A332" s="4"/>
+      <c r="B332" s="4">
+        <v>1002158</v>
+      </c>
+      <c r="C332" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D332" s="4">
+        <v>5</v>
+      </c>
+      <c r="E332" s="4">
+        <v>-11</v>
+      </c>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="16.5" spans="1:7">
+      <c r="A333" s="4"/>
+      <c r="B333" s="4">
+        <v>1002159</v>
+      </c>
+      <c r="C333" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D333" s="4">
+        <v>5</v>
+      </c>
+      <c r="E333" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="16.5" spans="1:7">
+      <c r="A334" s="4"/>
+      <c r="B334" s="4">
+        <v>1002160</v>
+      </c>
+      <c r="C334" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D334" s="4">
+        <v>5</v>
+      </c>
+      <c r="E334" s="4">
+        <v>-7</v>
+      </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="16.5" spans="1:7">
+      <c r="A335" s="4"/>
+      <c r="B335" s="4">
+        <v>1002161</v>
+      </c>
+      <c r="C335" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D335" s="4">
+        <v>5</v>
+      </c>
+      <c r="E335" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G335" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="16.5" spans="1:7">
+      <c r="A336" s="4"/>
+      <c r="B336" s="4">
+        <v>1002162</v>
+      </c>
+      <c r="C336" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D336" s="4">
+        <v>5</v>
+      </c>
+      <c r="E336" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="16.5" spans="1:7">
+      <c r="A337" s="4"/>
+      <c r="B337" s="4">
+        <v>1002163</v>
+      </c>
+      <c r="C337" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D337" s="4">
+        <v>5</v>
+      </c>
+      <c r="E337" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>敌方</t>
+        </is>
+      </c>
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="16.5" spans="1:7">
+      <c r="A338" s="4"/>
+      <c r="B338" s="4">
+        <v>1002164</v>
+      </c>
+      <c r="C338" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D338" s="4">
+        <v>5</v>
+      </c>
+      <c r="E338" s="4">
+        <v>1</v>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G338" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="16.5" spans="1:7">
+      <c r="A339" s="4"/>
+      <c r="B339" s="4">
+        <v>1002165</v>
+      </c>
+      <c r="C339" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D339" s="4">
+        <v>5</v>
+      </c>
+      <c r="E339" s="4">
+        <v>3</v>
+      </c>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="16.5" spans="1:7">
+      <c r="A340" s="4"/>
+      <c r="B340" s="4">
+        <v>1002166</v>
+      </c>
+      <c r="C340" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D340" s="4">
+        <v>5</v>
+      </c>
+      <c r="E340" s="4">
+        <v>5</v>
+      </c>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="16.5" spans="1:7">
+      <c r="A341" s="4"/>
+      <c r="B341" s="4">
+        <v>1002167</v>
+      </c>
+      <c r="C341" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D341" s="4">
+        <v>5</v>
+      </c>
+      <c r="E341" s="4">
+        <v>7</v>
+      </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="16.5" spans="1:7">
+      <c r="A342" s="4"/>
+      <c r="B342" s="4">
+        <v>1002168</v>
+      </c>
+      <c r="C342" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D342" s="4">
+        <v>5</v>
+      </c>
+      <c r="E342" s="4">
+        <v>9</v>
+      </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="16.5" spans="1:7">
+      <c r="A343" s="4"/>
+      <c r="B343" s="4">
+        <v>1002169</v>
+      </c>
+      <c r="C343" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D343" s="4">
+        <v>5</v>
+      </c>
+      <c r="E343" s="4">
+        <v>11</v>
+      </c>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G343" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="16.5" spans="1:7">
+      <c r="A344" s="4"/>
+      <c r="B344" s="4">
+        <v>1002170</v>
+      </c>
+      <c r="C344" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D344" s="4">
+        <v>5</v>
+      </c>
+      <c r="E344" s="4">
+        <v>13</v>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="16.5" spans="1:7">
+      <c r="A345" s="4"/>
+      <c r="B345" s="4">
+        <v>1002171</v>
+      </c>
+      <c r="C345" s="4">
+        <v>1002</v>
+      </c>
+      <c r="D345" s="4">
+        <v>5</v>
+      </c>
+      <c r="E345" s="4">
+        <v>15</v>
+      </c>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>己方</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
       </c>
     </row>
   </sheetData>
